--- a/docs/motive-outlines.xlsx
+++ b/docs/motive-outlines.xlsx
@@ -93,8 +93,8 @@
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="5" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -139,7 +139,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="111" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -160,12 +160,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" ht="48" customHeight="1">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The house runs because he wrote the rules and still checks them.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People bristle because nothing they do is quite correct.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been breaking those rules in public.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: fails the swap test (fits the Butler or Elder heir on the Emperor). Story: When he inherited he wrote the house rules into a book, and he still reads them out at Christmas. Rule nine was added after one embarrassing evening, and everyone knows who it was written for. Room: People check the book before they do anything. Talk: The victim was who rule nine was written for, and tonight broke it again, laughing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -186,12 +202,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He keeps a private list of who has disappointed him.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The house has learned to be careful in his silence.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had crossed him and then boasted about it.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: good kernel, but make it the upright story gone wrong. Story: The rule book has a back page of names, dates and what each person did, and he adds to it after dinner. Room: People watch to see whether he goes to the book tonight. Talk: The victim was added to the back page this evening, and underlined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -212,12 +244,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He treats family custom as law, and he will not let a new way in.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The younger ones find him immovable.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had mocked a family custom.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: too close to the Butler's Hierophant. Make it about the dinner itself. Story: Every dinner follows his grandfather's order of toasts, and he has never changed it. He would rather lose a guest than lose a toast. Room: The younger ones count the toasts down. Talk: The victim proposed a new toast out of turn, and the table drank to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -238,12 +286,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He invented a tradition on the spot to win an argument, then had it written down so it looked old.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People resent being beaten by a rule he made up.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to show the rule was new.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. The best Host row: concrete and funny. Talk could be sharper: the victim had found the paper it was written on, and the date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -264,12 +328,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He laid down one old family fight and is proud of the patience.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Everyone else thinks he is waiting for a better moment.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim was the person he was supposed to have forgiven.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: nearly the same as the Uncle's Hanged Man upright (each laid down an old quarrel). Make it a sacrifice for the house. Story: He sold the thing he loved most, his horses, to keep the roof on. He has never mentioned it, which is how everyone knows. Room: The family feels in his debt and resents it. Talk: The victim has been spending the money he gave up, on themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Host</t>
@@ -290,12 +370,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has held the house up for so long that he cannot put it down, and he mentions the weight.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People are tired of the sacrifice.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had offered to take the weight and been refused.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the new upright story. Story: He mentions the horses at every dinner now, as a small joke, and the joke is a bill. Room: People are tired of paying it. Talk: The victim told him in front of guests that nobody asked him to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -316,12 +412,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She feeds everyone and remembers who did not say thank you.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The house depends on her and resents the remembering.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been rude at her table.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP, add the object. Story: She keeps a seating book: where each guest sat, what they ate, and whether they thanked her. Talk is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -342,12 +454,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She keeps the house full of people who agree with her, and calls the rest ungrateful.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The rest of the house feels managed.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had disagreed with her in front of guests.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: generic. Make it the seating book gone sour. Story: The seating book now decides who is asked back. Anyone who disagreed with her moves down the table, then off it. Room: Everyone checks where they have been seated tonight. Talk: The victim was seated at the far end tonight, the last place before you stop being invited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="81" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -368,12 +496,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She believes a house this big should sparkle, and she is the one who makes it sparkle.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The practical people think the sparkle is a waste.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had made the house look shabby.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait, not a story. Story: She lit every lamp in the house for the first dinner since a bad year. Tonight is meant to prove the family is fine. Room: The practical ones know what the lamps cost. Talk: The victim said, loudly, that the family was not fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="81" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -394,12 +538,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She was told to tone the sparkle down, did so, and has not forgiven the evening for going dull.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People find the dulled brightness hard to live with.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one who told her to stop.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: make it the same evening gone wrong. Story: She knows the family is not fine, and the brightness is now a performance she cannot stop. Room: People find it hard to look at her smiling. Talk: The victim was the one person she told, and had started repeating it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -420,12 +580,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She has spent years matching people, including pairs who then refused to speak, and she still takes the credit.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The people she matched are not grateful.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been caught in one of her matches.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. Sharper talk: the victim was half of her proudest match, and had been seen walking out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hostess</t>
@@ -446,12 +622,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" ht="48" customHeight="1">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She nearly pledged the family to the wrong alliance, and she still carries the letter she did not send.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People worry she will arrange them next.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had refused a match she cared about.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP (the unsent letter is good). Sharper talk: the letter was about the victim, and the victim had found it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -472,12 +664,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has laid the same table for years and can tell which custom a guest has broken.</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The family finds him stricter than they are.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had offended the house's manners.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: overlaps the Host's Hierophant. Make it the service. Story: He has served this dinner the same way for thirty years: the silver, the order, the wine. He corrects a guest with a look, and the look is famous. Room: The family behaves better in front of him than alone. Talk: The victim sent the wine back twice, then did an impression of the look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -498,12 +706,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has looked the other way for this family so often that the silence is part of the service.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People are nervous about what he could say.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to mention something he was paid to forget.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. "The silence is part of the service" is strong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -524,12 +748,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He runs the staff the way the master runs the house, and he is the tidier of the two.</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The staff think he sides with the family. The family think he sides with the rules.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had left something uncounted.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP, sharpen. Story: He counts the silver every night and has never been a spoon short. Talk ("left something uncounted") is vague: the victim told the master his count was wrong, and the master believed the victim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -550,12 +790,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has the household books, and he has started applying the master's standards to the master.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">That is not what he was hired for, and the family has noticed.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had told him to stop noticing.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. The best borrowed-card row in the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -576,12 +832,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every door creaks differently, and he has never repeated what he heard in the passage.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People tell him things because he seems not to be listening.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had confided in him and then behaved as if it were still secret.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP, but split it from the Housekeeper and the Detective: the Butler HEARS (through doors), the Housekeeper SEES (laundry, grates, letters), the Detective USES (keeps it for the right moment). Story: He has heard every quarrel in this house through a door, and has never repeated one. Avoid creaks that say who left which room, which would be a where-were-they clue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Butler</t>
@@ -602,12 +874,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He knows what happens above stairs and below, and he is paid to look surprised.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The surprise has worn thin.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had assumed he would keep covering for them.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. Fits the Butler, as long as the Housekeeper's reversed row is reworked away from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="81" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -628,12 +916,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He can make a room like him with a coin and a story, and he needs the room to like him.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People enjoy him and do not quite trust the enjoyment.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one person who did not applaud.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: a trait. Give it stakes. Story: He was hired for tonight, his big trick needs a volunteer from the family, and another booking rides on it landing. Room: They enjoy him and suspect they are being worked. Talk: The victim refused to volunteer and told the table why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -654,12 +958,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A trick went wrong in front of people who mattered, and he talked his way out of it so well that nobody checked.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ones who noticed are still cross.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to ask how it was done.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="81" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -680,12 +1000,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He wants to be looked at kindly, and a good lamp is half the act.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The household treats him as decoration.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had upstaged him.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: fails the swap test (same as the Younger heir's Star). Story: He brought a poster of himself from one famous night years ago. He wants the house to remember he was a star once. Room: The household treats him as hired help, which he is. Talk: The victim remembered that night differently, and said so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -706,12 +1042,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" ht="48" customHeight="1">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The applause did not come, and he has been dimmer since, so that someone will ask him to brighten.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People find the sulk theatrical.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had forgotten to introduce him.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a sulk (one of five). Make it the poster gone wrong. Story: He was the assistant that night, not the star, and the poster has been touched up. Room: The few who know are embarrassed for him. Talk: The victim knew the real star.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="81" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -732,12 +1084,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" ht="48" customHeight="1">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He will find you exactly what you want, and the bill is very reasonable at first.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People who have used him are polite in a careful way.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to pay, or to refuse.</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: fails the swap test (it is the Financier's Devil). Make it the conjurer's trade. Story: Between shows he finds things for people (a ring, a letter, a ticket) and never says where from. Room: People who have used him are polite in a careful way. Talk: The victim asked him to find something, and he did.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conjurer</t>
@@ -758,12 +1126,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Everything he ever produced had a price, and some of those prices are still open.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He is charming and slightly desperate.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been holding one of his debts.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the upright story. Story: Some of what he found was stolen, and the owners have started asking. Room: Charming, and slightly desperate. Talk: The victim recognised one of his finds as their own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="81" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -784,12 +1168,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" ht="48" customHeight="1">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She notices everything and keeps it, and the house trusts her because she does not gossip.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People are a little afraid of how much she knows.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had let something slip in front of her.</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: overlaps the Butler. She SEES. Story: She does the laundry and the grates, so she knows what people wash out and what they burn. She has never said. Room: People are a little afraid of how much she knows. Talk: The victim burned something last week, and she cleaned the grate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -810,12 +1210,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" ht="48" customHeight="1">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She could say something, and she would rather watch them wonder.</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The family has started checking what they leave lying about.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had tried to buy her silence.</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP, small tweak so it is not the Butler's: she has started leaving things where they will be found, like a mended glove on a pillow. Talk is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="66" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -836,12 +1252,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" ht="48" customHeight="1">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She keeps to the back stairs, where the company is better and the opinions are fewer.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The front of the house thinks she is hiding.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had kept summoning her into the room.</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: She has one room at the top of the back stairs that is hers, with a lock she paid for herself. Room: The family thinks she keeps something up there. Talk: The victim wanted her room for a guest tonight and asked for the key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="66" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -862,12 +1294,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" ht="48" customHeight="1">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She has gone unnoticed for so long that she has started to mind, and the minding shows.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People are surprised she has a grievance.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had talked over her as if she were part of the furniture.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP the core, tie it to the room. Story: She was given the room instead of a rise in wages, and has just found out what the rise would have been. Talk: The victim joked that she should be grateful for the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="62" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -888,12 +1336,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" ht="48" customHeight="1">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She has closed more rooms than she has opened, and she finds the dust sheets restful.</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The family thinks she is packing the house away while they still live in it.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had wanted a shut room opened.</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. Her job turns Death into something real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="62" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Housekeeper</t>
@@ -914,12 +1378,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" ht="48" customHeight="1">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She has put this family into black more often than she thinks decent, and she will not let a goodbye be rushed.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People find her grim company.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been pretending an ending had not happened.</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="62" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -940,12 +1420,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" ht="48" customHeight="1">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He makes other people's wants possible, and he remembers the debt when they do not.</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Everyone is pleasant. Nobody is glad he came.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had owed him and been heard joking about it.</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="62" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -966,12 +1462,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" ht="48" customHeight="1">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An old bargain of his is coming due, and the terms were never written down.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has stopped sleeping properly, and the room can tell.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the other party to that bargain.</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. "The terms were never written down" is good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="62" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -1004,16 +1516,16 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The victim had put the house in disrepute, and he is the person who minds that. Talk points at him. It is not a clue.</t>
+          <t xml:space="preserve">The victim had put the house in disrepute, and he is the person who minds that.</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Example, from the theme session. Change it if this is wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
+          <t xml:space="preserve">KEEP. Your example, and the model for the rest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="62" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -1034,12 +1546,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" ht="48" customHeight="1">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He already has the real ledger, and he lets the house know it without quite showing it.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dislike has turned into fear.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been going to tell the others what was in it.</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. A good reversed: the same story escalated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="62" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -1060,12 +1588,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" ht="48" customHeight="1">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He is waiting on a sure thing that has already gone wrong, and he is being very calm about the loss.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People suspect the calm.</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one who advised the sure thing.</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="81" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Financier</t>
@@ -1086,12 +1630,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" ht="48" customHeight="1">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He backed a sure thing the wrong way up, and he has been explaining it ever since.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The explanation annoyed everyone who heard it the first time.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had laughed at the loss.</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: it is the upright story told twice. Make it gone wrong. Story: He has quietly covered the loss with money that was not his, and is waiting for the sure thing to come back before anyone counts. Room: The calm has cracks. Talk: The money he used was the victim's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="66" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1112,12 +1672,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" ht="48" customHeight="1">
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He prefers a closed door, and he has watched this family from a distance he recommends.</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">They hear the distance as a criticism.</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had tried to drag him into a family scene.</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: He was sent away from this family over a quarrel nobody explains to the children. He lives a mile off and comes to dinner once a year. Room: They hear the distance as a criticism. Talk: The victim was the other side of the quarrel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="81" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1138,12 +1714,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" ht="48" customHeight="1">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He went away to sulk and came back to find nobody had noticed, and he is still sulking about that.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The sulk is now the longest conversation he offers.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one who failed to notice.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a sulk. Tie it to the quarrel. Story: He came this year expecting the quarrel to be raised, nobody has mentioned it, and he keeps steering the talk towards it. Room: People keep changing the subject. Talk: The victim told him the quarrel was forgotten, and he heard it as an insult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="62" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1164,12 +1756,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He thinks the last chapter is the best one, and he will not hurry it, including other people's.</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The heirs find this inconvenient.</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been urging him to settle something.</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP, add the object. Story: He rewrites his will every year and will not be hurried, including about other people's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="81" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1190,12 +1798,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He keeps every grievance labelled, and he has sat through more goodbyes than he has accepted.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People dread being stored among the grievances.</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had asked him to let an old matter end.</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: overlaps the Host's list of grievances. Make it refusing to let go. Story: He has outlived everyone he was close to and keeps their things (a pipe, a hat, a letter), and he talks to them at dinner. Room: People find the empty chairs hard. Talk: The victim threw one of those things away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="66" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1216,12 +1840,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" ht="48" customHeight="1">
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He laid the old quarrel down once, halfway through, and nobody trusted it.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">They still do not trust the truce.</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been on the other side and had believed the truce.</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: nearly the same as the Host's Hanged Man upright. Make it waiting. Story: He has waited twenty years for an apology and arranged his life around it. Room: They wish he would let it go. Talk: The victim owed the apology and made a joke instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="66" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncle</t>
@@ -1242,12 +1882,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" ht="48" customHeight="1">
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has hovered at the edge of this family for years, waiting to be asked in, and the waiting has become the point.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People wish he would either leave or sit down.</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had finally told him to go.</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, tie it to the upright story. Story: He finally got the apology last year, it changed nothing, and now he does not know what to want. Room: He is oddly lost, and it unsettles them. Talk: The victim gave the apology and expected thanks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="62" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1268,12 +1924,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" ht="48" customHeight="1">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He drew up a plan for the whole family, colour-coded, without being asked.</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Everyone has a place in it. Nobody agreed.</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had refused their place in the plan.</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. The colour-coded plan is concrete and funny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="62" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1294,12 +1966,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" ht="48" customHeight="1">
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has been promised the house since he was small, and he has started correcting the promise in public.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The patience in the room is thin.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had suggested he wait.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="81" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1320,12 +2008,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" ht="48" customHeight="1">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He learned how a house should be run from someone who never let him forget the lesson, and he is ready to apply it.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The present way of doing things feels the criticism.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had called him unready.</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: generic. Story: He has started giving the staff orders as if the house were already his, and some of them obey. Room: The present master feels it, and the staff do not know whom to answer. Talk: The victim countermanded one of his orders in front of the staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="66" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1346,12 +2050,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" ht="48" customHeight="1">
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He rearranged how the family ought to stand, with himself at the front, and he was caught at it.</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People have not forgotten.</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one who put him back in his place.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: abstract. Give it an object. Story: He had the family portrait re-hung with himself in the middle. Room: Nobody has moved it back, and everybody notices it. Talk: The victim was the one who moved it back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="81" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1372,12 +2092,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He will do a deal to have the house sooner, and he thinks the terms are generous.</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The people on the other side of the deal are less sure.</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to refuse him.</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: vague (a deal with whom?), and it overlaps the reversed row. Story: He has a buyer lined up for the land the day it is his, and has already taken a deposit. Room: The people who love the land are less sure. Talk: The victim found the buyer's letter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="62" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elder heir</t>
@@ -1398,12 +2134,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" ht="48" customHeight="1">
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He has borrowed against the future so often that the future has started sending reminders.</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He is bright, and short of cash.</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been one of the reminders.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. "The future has started sending reminders" is good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="81" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1424,12 +2176,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He can make the stern ones laugh, and he has rarely had to want a thing for long.</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The serious half of the family thinks the house indulges him.</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to make him earn something.</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: He has never had to work. This year he was given a place in the family business, and he has been in twice. Room: The serious half of the family thinks the house indulges him. Talk: The victim was writing a report on him, and he had seen it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="66" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1450,12 +2218,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" ht="48" customHeight="1">
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He sulked until a party was called off, and he still thinks the party was at fault.</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People are weary of the light going out.</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one who told him no.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the job. Story: He quit and threw a party to celebrate, and the family paid for it. Room: People are weary of the light going on and off. Talk: The victim refused to pay the bill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="66" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1476,12 +2260,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" ht="48" customHeight="1">
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He falls for people easily, and never for the same one twice.</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The house has learned to recognise the look.</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the latest person, or the person who already had a claim on them.</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: He is secretly engaged to someone the family would not approve of, and wears the ring on a chain. Room: The house has noticed him watching for the post. Talk: The victim had found out who it was.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="66" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1502,12 +2302,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" ht="48" customHeight="1">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He answered a proposal with "we'll see," and the seeing has lasted for years.</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Someone in the room is tired of being a maybe.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one left waiting.</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP the core, tie it to the upright story. Story: He said "we'll see" to one proposal and yes to another, and neither knows about the other. Talk: The victim was one of the two, or had found out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="96" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1528,12 +2344,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" ht="48" customHeight="1">
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He expects something lovely to arrive, and he is happy to be looked at while it does.</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strangers are charmed. The family is tired.</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had failed to admire him.</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: fails the swap test (the same as the Conjurer's Star). Story: He has been told since he was small that he will be famous for something. He has tried painting, poetry and the stage, and tonight he reads his poem after dinner. Room: Strangers are charmed and the family braces. Talk: The victim read the poem earlier and laughed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="81" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Younger heir</t>
@@ -1554,12 +2386,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" ht="48" customHeight="1">
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Everyone says he will go far, and he would like to go further, in a better carriage.</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The promise feels like a delay.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the one keeping him from the better carriage.</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the upright story. Story: Nobody came to his last reading. He has decided the family holds him back, and he wants his share now so he can be brilliant elsewhere. Room: The promise feels like a delay. Talk: The victim was the one keeping his share in trust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="66" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1580,12 +2428,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" ht="48" customHeight="1">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He weighs a thing twice, and he has solved worse puzzles than a dinner.</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The guests feel examined.</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had noticed him notice something that did not fit.</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: He is here as a guest, but he was called to this house once before, professionally, and the case was never closed. Room: The guests feel examined. Talk: The victim was a suspect in the old case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="62" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1606,12 +2470,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He settled on his answer before the facts arrived, and then he sent for the facts.</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anyone he has accused once does not relax.</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been about to prove him wrong.</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP. "Then he sent for the facts" is good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="81" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1632,12 +2512,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He knows what to leave unsaid until the right moment, and he enjoys having the moment in his pocket.</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People tell him less than they mean to.</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had realised he was saving something up.</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: overlaps the Butler and the Housekeeper. He USES what he knows. Story: He carries a notebook with a page for each guest, and lets them watch him turn to theirs. Room: People tell him less than they mean to. Talk: The victim saw what was on their own page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="66" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1658,12 +2554,28 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" ht="48" customHeight="1">
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He keeps what he is told, and he lets other people discover it at a bad moment.</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The room has started to wonder whose turn is next.</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had given him a secret and then seen him smile.</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the notebook. Story: He has started trading pages for favours. Room: The room wonders whose page is next. Talk: The victim paid him to keep a page shut, and he opened it anyway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="81" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1684,12 +2596,28 @@
           <t xml:space="preserve">Upright</t>
         </is>
       </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" ht="48" customHeight="1">
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He does his thinking where nobody can help, and he prefers it.</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The others feel shut out of their own evening.</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had insisted on staying while he thought.</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK: a trait. Story: He retired after a case went wrong and swore off company. He came tonight only because the invitation said it was a favour. Room: The others feel shut out of their own evening. Talk: The victim sent the invitation, and he wants to know why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="66" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Detective</t>
@@ -1710,10 +2638,26 @@
           <t xml:space="preserve">Reversed</t>
         </is>
       </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He thinks alone because, as he has mentioned, nobody else can keep up.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The insult is quiet and complete.</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The victim had been the person who could not keep up, and had minded being told so.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REWORK, light: tie it to the case that went wrong. Story: He says the case failed because the others were slow, and he has told tonight's guests so. Room: The insult is quiet and complete. Talk: The victim was a witness in that case, and slow.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H61"/>
@@ -1730,14 +2674,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motive outlines, before any lines are rewritten</t>
+          <t xml:space="preserve">Motive outlines. Drafts to edit, before any lines are rewritten.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill the yellow cells. Grey cells are the combinations, already fixed from the guest and card list.</t>
+          <t xml:space="preserve">The yellow cells are drafts. Change any of them. The grey cells are the combinations, already fixed.</t>
         </is>
       </c>
     </row>
@@ -1751,7 +2695,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Story: one or two sentences. What is true of this person when this is the card she hears.</t>
+          <t xml:space="preserve">Story: what is true of this person when this is the card she hears.</t>
         </is>
       </c>
     </row>
@@ -1779,14 +2723,14 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Financier on the Emperor, upright, is the example. Change it if it is wrong. Every other yellow cell is empty on purpose.</t>
+          <t xml:space="preserve">Notes is empty, for your own comments.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spoken lines, and the ending sentences, come after this sheet is filled. Nothing in the game changes until then.</t>
+          <t xml:space="preserve">Spoken lines, and the ending sentences, come after you are happy with this sheet. Nothing in the game changes until then.</t>
         </is>
       </c>
     </row>
